--- a/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du déjeuner. Idriss s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a un morceau de poivron jaune. Idriss le regarde. Le poivron est lisse. Il sent le jardin. Maman sourit. Maman dit : tu peux goûter. Juste une petite portion. Idriss prend une petite bouchée. Il la met dans sa bouche. C'est un peu sucré. Idriss dit : c'est sucré, maman. Il a su nommer le goût. Maman dit : merci d'avoir goûté. Une petite portion, c'est déjà bien.</t>
+          <t>C'est l'heure du déjeuner. Idriss s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a un morceau de poivron jaune. Idriss le regarde. Le poivron est lisse. Il sent le jardin. Maman sourit. Tu peux goûter. Juste une petite portion. Idriss prend une petite bouchée. Il la met dans sa bouche. C'est un peu sucré. C'est sucré, maman. Il a su nommer le goût. Merci d'avoir goûté. Une petite portion, c'est déjà bien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est l'heure du déjeuner. Idriss s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a un morceau de poivron jaune. Idriss le regarde. Le poivron est lisse. Il sent le jardin. Maman sourit.
+maman|Tu peux goûter. Juste une petite portion.
+narrateur|Idriss prend une petite bouchée. Il la met dans sa bouche. C'est un peu sucré.
+enfant-m|C'est sucré, maman. Il a su nommer le goût.
+maman|Merci d'avoir goûté.
+narrateur|Une petite portion, c'est déjà bien.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss goûte le poivron. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss a goûté. Il a nommé le goût. Maman est là. Une petite portion, c'est assez.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss boit une gorgée d'eau. Le poivron reste dans l'assiette. Idriss dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Une petite portion, c'est déjà bien.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Idriss goûte le poivron. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Idriss a goûté. Il a nommé le goût. Maman est là. Une petite portion, c'est assez.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Idriss boit une gorgée d'eau. Le poivron reste dans l'assiette. Idriss dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le poivron jaune d'Idriss</t>
+          <t>Le carré jaune</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un carré de soleil jaune dort sur la nappe. Raphaël croit que c'est un lampion. C'est un poivron. Il s'assoit. Il goûte une petite bouchée sucrée.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du déjeuner. Idriss s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a un morceau de poivron jaune. Idriss le regarde. Le poivron est lisse. Il sent le jardin. Maman sourit. Tu peux goûter. Juste une petite portion. Idriss prend une petite bouchée. Il la met dans sa bouche. C'est un peu sucré. C'est sucré, maman. Il a su nommer le goût. Merci d'avoir goûté. Une petite portion, c'est déjà bien.</t>
+          <t>La vitre de la cuisine est embuée. Raphaël trace un petit trait. Le trait fait une fenêtre. Dehors, le village est calme. Un chat passe sur le muret. Raphaël vit ici, avec maman. Papa range des pots, tout près. Ça sent le poivron grillé. Un carré jaune dort sur la nappe. Il est chaud, tout lisse. La nappe a des points blancs. Maman, c'est un lampion ? Viens voir, Raphaël. C'est un poivron. Un poivron jaune. Raphaël pousse la porte. La porte fait un petit bruit. Maman est près de la planche. Viens t'asseoir. Raphaël va vers sa chaise. Il tire un peu la chaise. Il s'assoit près de maman. Il pose les pieds par terre. Bravo, Raphaël. Tu es bien assis. On est ensemble, à table. Sa chaise ne bouge plus. Une mouche bourdonne dehors. Tu as entendu la mouche ? Oui, maman. Une assiette attend Raphaël. Dans l'assiette, du riz. À côté, un morceau jaune. Le poivron est lisse. Il brille un peu. Il sent le jardin ! Oui. Le jardin, au soleil. Tu as bien regardé. Raphaël pose les mains sur la table. Le carré jaune touche le poivron. Raphaël se penche tout près. Ça sent le jardin. Ça sent le jardin, hein ? Oui. Le jardin. Il a quel goût ? Tu veux goûter ? Une petite bouchée. Juste une petite portion. Raphaël prend une petite bouchée. Il goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1329,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est l'heure du déjeuner. Idriss s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a un morceau de poivron jaune. Idriss le regarde. Le poivron est lisse. Il sent le jardin. Maman sourit.
-maman|Tu peux goûter. Juste une petite portion.
-narrateur|Idriss prend une petite bouchée. Il la met dans sa bouche. C'est un peu sucré.
-enfant-m|C'est sucré, maman. Il a su nommer le goût.
-maman|Merci d'avoir goûté.
-narrateur|Une petite portion, c'est déjà bien.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine est embuée.
+narrateur|Raphaël trace un petit trait.
+narrateur|Le trait fait une fenêtre.
+narrateur|Dehors, le village est calme.
+narrateur|Un chat passe sur le muret.
+narrateur|Raphaël vit ici, avec maman.
+narrateur|Papa range des pots, tout près.
+narrateur|Ça sent le poivron grillé.
+narrateur|Un carré jaune dort sur la nappe.
+narrateur|Il est chaud, tout lisse.
+narrateur|La nappe a des points blancs.
+enfant-m|Maman, c'est un lampion ?
+maman|Viens voir, Raphaël.
+maman|C'est un poivron.
+maman|Un poivron jaune.
+narrateur|Raphaël pousse la porte.
+narrateur|La porte fait un petit bruit.
+narrateur|Maman est près de la planche.
+maman|Viens t'asseoir.
+narrateur|Raphaël va vers sa chaise.
+narrateur|Il tire un peu la chaise.
+narrateur|Il s'assoit près de maman.
+narrateur|Il pose les pieds par terre.
+maman|Bravo, Raphaël.
+maman|Tu es bien assis.
+maman|On est ensemble, à table.
+narrateur|Sa chaise ne bouge plus.
+narrateur|Une mouche bourdonne dehors.
+maman|Tu as entendu la mouche ?
+enfant-m|Oui, maman.
+narrateur|Une assiette attend Raphaël.
+narrateur|Dans l'assiette, du riz.
+narrateur|À côté, un morceau jaune.
+narrateur|Le poivron est lisse.
+narrateur|Il brille un peu.
+enfant-m|Il sent le jardin !
+maman|Oui.
+maman|Le jardin, au soleil.
+maman|Tu as bien regardé.
+narrateur|Raphaël pose les mains sur la table.
+narrateur|Le carré jaune touche le poivron.
+narrateur|Raphaël se penche tout près.
+narrateur|Ça sent le jardin.
+maman|Ça sent le jardin, hein ?
+enfant-m|Oui. Le jardin.
+enfant-m|Il a quel goût ?
+maman|Tu veux goûter ?
+maman|Une petite bouchée.
+maman|Juste une petite portion.
+narrateur|Raphaël prend une petite bouchée.
+narrateur|Il goûte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>porte,chaise</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Idriss goûte le poivron. Que fait-il ?</t>
+          <t>Raphaël goûte. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Idriss goûte le poivron. Que fait-il ?</t>
+          <t>narrateur|Raphaël goûte.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Idriss a goûté. Il a nommé le goût. Maman est là. Une petite portion, c'est assez.</t>
+          <t>Raphaël mâche. Il mâche encore un peu. Il est toujours assis. C'est sucré, maman. Un peu doux. Comme le soleil. Oui. Doux et sucré. Bravo, Raphaël. Tu as nommé le goût. C'est du bon travail. Un bout jaune reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1740,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Idriss a goûté. Il a nommé le goût. Maman est là. Une petite portion, c'est assez.</t>
+          <t>narrateur|Raphaël mâche.
+narrateur|Il mâche encore un peu.
+narrateur|Il est toujours assis.
+enfant-m|C'est sucré, maman.
+enfant-m|Un peu doux.
+enfant-m|Comme le soleil.
+maman|Oui. Doux et sucré.
+maman|Bravo, Raphaël.
+maman|Tu as nommé le goût.
+maman|C'est du bon travail.
+narrateur|Un bout jaune reste dans l'assiette.
+maman|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Idriss boit une gorgée d'eau. Le poivron reste dans l'assiette. Idriss dit merci.</t>
+          <t>Raphaël reste à table. Maman verse un peu d'eau. L'eau fait un petit bruit. Tu veux un peu d'eau ? Raphaël boit une gorgée. Le poivron reste dans l'assiette. Raphaël le regarde. Il brille encore. Une petite portion, c'est déjà bien. Merci, maman. Merci, Raphaël. On reste encore un peu ensemble ? Oui. Raphaël reste assis. La cuisine est calme. Tu es encore bien assis. Bravo. Le carré jaune attend.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,7 +1915,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Idriss boit une gorgée d'eau. Le poivron reste dans l'assiette. Idriss dit merci.</t>
+          <t>narrateur|Raphaël reste à table.
+narrateur|Maman verse un peu d'eau.
+narrateur|L'eau fait un petit bruit.
+maman|Tu veux un peu d'eau ?
+narrateur|Raphaël boit une gorgée.
+narrateur|Le poivron reste dans l'assiette.
+narrateur|Raphaël le regarde.
+narrateur|Il brille encore.
+maman|Une petite portion, c'est déjà bien.
+enfant-m|Merci, maman.
+maman|Merci, Raphaël.
+maman|On reste encore un peu ensemble ?
+enfant-m|Oui.
+narrateur|Raphaël reste assis.
+narrateur|La cuisine est calme.
+maman|Tu es encore bien assis.
+maman|Bravo.
+narrateur|Le carré jaune attend.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai goûté une petite bouchée. C'était sucré. Bravo. Tu as fait du bon travail. On était assis, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai goûté une petite bouchée.
+enfant-m|C'était sucré.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|On était assis, ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est l'heure du déjeuner. Idriss s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a un morceau de poivron jaune. Idriss le regarde. Le poivron est lisse. Il sent le jardin. Maman sourit. Maman dit : tu peux &lt;emphasis level="moderate"&gt;goûter&lt;/emphasis&gt;. Juste une petite portion. Idriss prend une petite bouchée. Il la met dans sa bouche. C'est un peu sucré. Idriss dit : c'est sucré, maman. Il a su nommer le goût. Maman dit : merci d'avoir goûté. Une petite portion, c'est déjà bien.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine est embuée. Raphaël trace un petit trait. Le trait fait une fenêtre. Dehors, le village est calme. Un chat passe sur le muret. Raphaël vit ici, avec maman. Papa range des pots, tout près. Ça sent le poivron grillé. Un carré jaune dort sur la nappe. Il est chaud, tout lisse. La nappe a des points blancs. Maman, c'est un lampion ? Viens voir, Raphaël. C'est un poivron. Un poivron jaune. Raphaël pousse la porte. La porte fait un petit bruit. Maman est près de la planche. Viens t'asseoir. Raphaël va vers sa chaise. Il tire un peu la chaise. Il s'assoit près de maman. Il pose les pieds par terre. Bravo, Raphaël. Tu es bien assis. On est ensemble, à table. Sa chaise ne bouge plus. Une mouche bourdonne dehors. Tu as entendu la mouche ? Oui, maman. Une assiette attend Raphaël. Dans l'assiette, du riz. À côté, un morceau jaune. Le poivron est lisse. Il brille un peu. Il sent le jardin ! Oui. Le jardin, au soleil. Tu as bien regardé. Raphaël pose les mains sur la table. Le carré jaune touche le poivron. Raphaël se penche tout près. Ça sent le jardin. Ça sent le jardin, hein ? Oui. Le jardin. Il a quel goût ? Tu veux goûter ? Une petite bouchée. Juste une petite portion. Raphaël prend une petite bouchée. Il goûte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Idriss goûte le poivron. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël goûte. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1571,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël mâche. Il mâche encore un peu. Il est toujours assis. C'est sucré, maman. Un peu doux. Comme le soleil. Oui. Doux et sucré. Bravo, Raphaël. Tu as nommé le goût. C'est du bon travail. Un bout jaune reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
+          <t>Raphaël mâche. Il mâche encore un peu. Il est toujours assis. C'est sucré, maman. Un peu doux. Comme le soleil. Oui. Doux et sucré. Bravo, Raphaël. Tu as nommé le goût. Un bout jaune reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Idriss a goûté. Il a nommé le goût. Maman est là. Une &lt;emphasis level="moderate"&gt;petite&lt;/emphasis&gt; portion, c'est assez.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël mâche. Il mâche encore un peu. Il est toujours assis. C'est sucré, maman. Un peu doux. Comme le soleil. Oui. Doux et sucré. Bravo, Raphaël. Tu as nommé le goût. Un bout jaune reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,12 +1748,10 @@
 maman|Oui. Doux et sucré.
 maman|Bravo, Raphaël.
 maman|Tu as nommé le goût.
-maman|C'est du bon travail.
 narrateur|Un bout jaune reste dans l'assiette.
 maman|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1784,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Idriss boit une gorgée d'eau. Le poivron reste dans l'assiette. Idriss dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël reste à table. Maman verse un peu d'eau. L'eau fait un petit bruit. Tu veux un peu d'eau ? Raphaël boit une gorgée. Le poivron reste dans l'assiette. Raphaël le regarde. Il brille encore. Une petite portion, c'est déjà bien. Merci, maman. Merci, Raphaël. On reste encore un peu ensemble ? Oui. Raphaël reste assis. La cuisine est calme. Tu es encore bien assis. Bravo. Le carré jaune attend.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1932,6 @@
 narrateur|Le carré jaune attend.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai goûté une petite bouchée. C'était sucré. Bravo. Tu as fait du bon travail. On était assis, ensemble. L'histoire est finie.</t>
+          <t>J'ai goûté une petite bouchée. C'était sucré. Bravo. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai goûté une petite bouchée. C'était sucré. Bravo. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2099,9 @@
           <t>enfant-m|J'ai goûté une petite bouchée.
 enfant-m|C'était sucré.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-maman|On était assis, ensemble.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On était assis, ensemble.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-05.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Idriss, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
